--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3051,6 +3051,2066 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120454262</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>506386</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7137645</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120454446</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>506409</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7137583</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120455044</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>506457</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7137369</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120455339</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>506407</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7137248</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120454514</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>506386</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7137593</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120454929</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>506479</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7137395</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120455249</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506409</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7137328</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120455279</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506406</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7137298</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120454696</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506430</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7137522</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120454691</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>353</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>506429</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7137523</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120454245</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>506382</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7137641</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120454435</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506404</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7137583</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120455376</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506425</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7137243</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120454398</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90591</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>506414</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7137627</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120455240</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>506406</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7137340</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120454335</v>
+      </c>
+      <c r="B38" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>53</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506408</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7137649</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120454852</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>506472</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7137475</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120454291</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506401</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7137641</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120455183</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506424</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7137367</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120454579</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506394</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7137587</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -3053,7 +3053,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120454262</v>
+        <v>120454245</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506386</v>
+        <v>506382</v>
       </c>
       <c r="R23" t="n">
-        <v>7137645</v>
+        <v>7137641</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120454446</v>
+        <v>120454579</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506409</v>
+        <v>506394</v>
       </c>
       <c r="R24" t="n">
-        <v>7137583</v>
+        <v>7137587</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120455044</v>
+        <v>120454435</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,42 +3278,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506457</v>
+        <v>506404</v>
       </c>
       <c r="R25" t="n">
-        <v>7137369</v>
+        <v>7137583</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3369,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120455339</v>
+        <v>120454335</v>
       </c>
       <c r="B26" t="n">
-        <v>96885</v>
+        <v>95478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3381,25 +3376,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506407</v>
+        <v>506408</v>
       </c>
       <c r="R26" t="n">
-        <v>7137248</v>
+        <v>7137649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3471,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120454514</v>
+        <v>120454929</v>
       </c>
       <c r="B27" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3483,25 +3478,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3511,13 +3506,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506386</v>
+        <v>506479</v>
       </c>
       <c r="R27" t="n">
-        <v>7137593</v>
+        <v>7137395</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3573,10 +3568,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120454929</v>
+        <v>120455044</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,37 +3584,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506479</v>
+        <v>506457</v>
       </c>
       <c r="R28" t="n">
-        <v>7137395</v>
+        <v>7137369</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120455249</v>
+        <v>120454398</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>90591</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506409</v>
+        <v>506414</v>
       </c>
       <c r="R29" t="n">
-        <v>7137328</v>
+        <v>7137627</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120455279</v>
+        <v>120455249</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3789,25 +3789,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506406</v>
+        <v>506409</v>
       </c>
       <c r="R30" t="n">
-        <v>7137298</v>
+        <v>7137328</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120454696</v>
+        <v>120454262</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,13 +3919,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506430</v>
+        <v>506386</v>
       </c>
       <c r="R31" t="n">
-        <v>7137522</v>
+        <v>7137645</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3955,6 +3955,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3981,10 +3986,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454691</v>
+        <v>120454514</v>
       </c>
       <c r="B32" t="n">
-        <v>78187</v>
+        <v>79652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3993,25 +3998,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,13 +4026,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506429</v>
+        <v>506386</v>
       </c>
       <c r="R32" t="n">
-        <v>7137523</v>
+        <v>7137593</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4083,10 +4088,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120454245</v>
+        <v>120454696</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4104,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,13 +4128,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506382</v>
+        <v>506430</v>
       </c>
       <c r="R33" t="n">
-        <v>7137641</v>
+        <v>7137522</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4159,11 +4164,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120454435</v>
+        <v>120455339</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4202,25 +4202,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506404</v>
+        <v>506407</v>
       </c>
       <c r="R34" t="n">
-        <v>7137583</v>
+        <v>7137248</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120455376</v>
+        <v>120455183</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4308,21 +4308,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506425</v>
+        <v>506424</v>
       </c>
       <c r="R35" t="n">
-        <v>7137243</v>
+        <v>7137367</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4368,6 +4368,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4394,10 +4399,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120454398</v>
+        <v>120455240</v>
       </c>
       <c r="B36" t="n">
-        <v>90591</v>
+        <v>79624</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4406,25 +4411,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4434,10 +4439,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506414</v>
+        <v>506406</v>
       </c>
       <c r="R36" t="n">
-        <v>7137627</v>
+        <v>7137340</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4496,10 +4501,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120455240</v>
+        <v>120454691</v>
       </c>
       <c r="B37" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4512,21 +4517,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4536,13 +4541,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506406</v>
+        <v>506429</v>
       </c>
       <c r="R37" t="n">
-        <v>7137340</v>
+        <v>7137523</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4598,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454335</v>
+        <v>120454852</v>
       </c>
       <c r="B38" t="n">
-        <v>95478</v>
+        <v>79131</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4614,21 +4619,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4638,13 +4643,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506408</v>
+        <v>506472</v>
       </c>
       <c r="R38" t="n">
-        <v>7137649</v>
+        <v>7137475</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4700,10 +4705,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120454852</v>
+        <v>120455376</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4716,21 +4721,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4740,13 +4745,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506472</v>
+        <v>506425</v>
       </c>
       <c r="R39" t="n">
-        <v>7137475</v>
+        <v>7137243</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4802,10 +4807,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454291</v>
+        <v>120455279</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4818,21 +4823,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4842,10 +4847,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506401</v>
+        <v>506406</v>
       </c>
       <c r="R40" t="n">
-        <v>7137641</v>
+        <v>7137298</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,10 +4909,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120455183</v>
+        <v>120454446</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4920,21 +4925,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4944,10 +4949,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506424</v>
+        <v>506409</v>
       </c>
       <c r="R41" t="n">
-        <v>7137367</v>
+        <v>7137583</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,11 +4985,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5011,7 +5011,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454579</v>
+        <v>120454291</v>
       </c>
       <c r="B42" t="n">
         <v>78542</v>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506394</v>
+        <v>506401</v>
       </c>
       <c r="R42" t="n">
-        <v>7137587</v>
+        <v>7137641</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -3053,7 +3053,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120454245</v>
+        <v>120454262</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506382</v>
+        <v>506386</v>
       </c>
       <c r="R23" t="n">
-        <v>7137641</v>
+        <v>7137645</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120454579</v>
+        <v>120454691</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506394</v>
+        <v>506429</v>
       </c>
       <c r="R24" t="n">
-        <v>7137587</v>
+        <v>7137523</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120454435</v>
+        <v>120455183</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,21 +3278,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506404</v>
+        <v>506424</v>
       </c>
       <c r="R25" t="n">
-        <v>7137583</v>
+        <v>7137367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,6 +3338,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120454335</v>
+        <v>120455376</v>
       </c>
       <c r="B26" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3380,21 +3385,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3404,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506408</v>
+        <v>506425</v>
       </c>
       <c r="R26" t="n">
-        <v>7137649</v>
+        <v>7137243</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3466,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120454929</v>
+        <v>120455044</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3482,37 +3487,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506479</v>
+        <v>506457</v>
       </c>
       <c r="R27" t="n">
-        <v>7137395</v>
+        <v>7137369</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120455044</v>
+        <v>120454929</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3584,42 +3594,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506457</v>
+        <v>506479</v>
       </c>
       <c r="R28" t="n">
-        <v>7137369</v>
+        <v>7137395</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3675,10 +3680,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120454398</v>
+        <v>120455240</v>
       </c>
       <c r="B29" t="n">
-        <v>90591</v>
+        <v>79624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3687,25 +3692,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3720,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506414</v>
+        <v>506406</v>
       </c>
       <c r="R29" t="n">
-        <v>7137627</v>
+        <v>7137340</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3777,10 +3782,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120455249</v>
+        <v>120454435</v>
       </c>
       <c r="B30" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3789,25 +3794,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3817,13 +3822,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506409</v>
+        <v>506404</v>
       </c>
       <c r="R30" t="n">
-        <v>7137328</v>
+        <v>7137583</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120454262</v>
+        <v>120455249</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79658</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3891,25 +3896,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506386</v>
+        <v>506409</v>
       </c>
       <c r="R31" t="n">
-        <v>7137645</v>
+        <v>7137328</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3955,11 +3960,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3986,10 +3986,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454514</v>
+        <v>120454398</v>
       </c>
       <c r="B32" t="n">
-        <v>79652</v>
+        <v>90591</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4002,21 +4002,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506386</v>
+        <v>506414</v>
       </c>
       <c r="R32" t="n">
-        <v>7137593</v>
+        <v>7137627</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120454696</v>
+        <v>120454514</v>
       </c>
       <c r="B33" t="n">
-        <v>79160</v>
+        <v>79652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4100,25 +4100,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4128,13 +4128,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506430</v>
+        <v>506386</v>
       </c>
       <c r="R33" t="n">
-        <v>7137522</v>
+        <v>7137593</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4190,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120455339</v>
+        <v>120454291</v>
       </c>
       <c r="B34" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4202,25 +4202,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506407</v>
+        <v>506401</v>
       </c>
       <c r="R34" t="n">
-        <v>7137248</v>
+        <v>7137641</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120455183</v>
+        <v>120454446</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4308,21 +4308,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506424</v>
+        <v>506409</v>
       </c>
       <c r="R35" t="n">
-        <v>7137367</v>
+        <v>7137583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4368,11 +4368,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4399,10 +4394,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120455240</v>
+        <v>120454579</v>
       </c>
       <c r="B36" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4415,21 +4410,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4439,10 +4434,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506406</v>
+        <v>506394</v>
       </c>
       <c r="R36" t="n">
-        <v>7137340</v>
+        <v>7137587</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4501,10 +4496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120454691</v>
+        <v>120455279</v>
       </c>
       <c r="B37" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4517,21 +4512,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4541,10 +4536,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506429</v>
+        <v>506406</v>
       </c>
       <c r="R37" t="n">
-        <v>7137523</v>
+        <v>7137298</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,10 +4598,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454852</v>
+        <v>120454335</v>
       </c>
       <c r="B38" t="n">
-        <v>79131</v>
+        <v>95478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4619,21 +4614,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4643,13 +4638,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506472</v>
+        <v>506408</v>
       </c>
       <c r="R38" t="n">
-        <v>7137475</v>
+        <v>7137649</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4705,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120455376</v>
+        <v>120454696</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4721,21 +4716,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506425</v>
+        <v>506430</v>
       </c>
       <c r="R39" t="n">
-        <v>7137243</v>
+        <v>7137522</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4807,10 +4802,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120455279</v>
+        <v>120454245</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4823,21 +4818,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4847,13 +4842,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506406</v>
+        <v>506382</v>
       </c>
       <c r="R40" t="n">
-        <v>7137298</v>
+        <v>7137641</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4883,6 +4878,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4909,10 +4909,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120454446</v>
+        <v>120455339</v>
       </c>
       <c r="B41" t="n">
-        <v>79624</v>
+        <v>96885</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4921,25 +4921,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506409</v>
+        <v>506407</v>
       </c>
       <c r="R41" t="n">
-        <v>7137583</v>
+        <v>7137248</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454291</v>
+        <v>120454852</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5027,21 +5027,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506401</v>
+        <v>506472</v>
       </c>
       <c r="R42" t="n">
-        <v>7137641</v>
+        <v>7137475</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4598,10 +4598,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454335</v>
+        <v>120454696</v>
       </c>
       <c r="B38" t="n">
-        <v>95478</v>
+        <v>79160</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4614,21 +4614,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506408</v>
+        <v>506430</v>
       </c>
       <c r="R38" t="n">
-        <v>7137649</v>
+        <v>7137522</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120454696</v>
+        <v>120454335</v>
       </c>
       <c r="B39" t="n">
-        <v>79160</v>
+        <v>95478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506430</v>
+        <v>506408</v>
       </c>
       <c r="R39" t="n">
-        <v>7137522</v>
+        <v>7137649</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5111,6 +5111,113 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120523986</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lidsjöberg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>506423</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7137364</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -3053,10 +3053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120454262</v>
+        <v>120455339</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3065,25 +3065,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3093,13 +3093,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506386</v>
+        <v>506407</v>
       </c>
       <c r="R23" t="n">
-        <v>7137645</v>
+        <v>7137248</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3129,11 +3129,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3262,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120455183</v>
+        <v>120454435</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,21 +3273,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506424</v>
+        <v>506404</v>
       </c>
       <c r="R25" t="n">
-        <v>7137367</v>
+        <v>7137583</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,11 +3333,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3471,10 +3461,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120455044</v>
+        <v>120455279</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,42 +3477,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506457</v>
+        <v>506406</v>
       </c>
       <c r="R27" t="n">
-        <v>7137369</v>
+        <v>7137298</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3578,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120454929</v>
+        <v>120454245</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3594,21 +3579,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3618,13 +3603,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506479</v>
+        <v>506382</v>
       </c>
       <c r="R28" t="n">
-        <v>7137395</v>
+        <v>7137641</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3654,6 +3639,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,10 +3670,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120455240</v>
+        <v>120455249</v>
       </c>
       <c r="B29" t="n">
-        <v>79624</v>
+        <v>79658</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3692,25 +3682,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3720,10 +3710,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506406</v>
+        <v>506409</v>
       </c>
       <c r="R29" t="n">
-        <v>7137340</v>
+        <v>7137328</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3782,10 +3772,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120454435</v>
+        <v>120454929</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3798,21 +3788,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3822,10 +3812,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506404</v>
+        <v>506479</v>
       </c>
       <c r="R30" t="n">
-        <v>7137583</v>
+        <v>7137395</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,10 +3874,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120455249</v>
+        <v>120455044</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,41 +3886,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506409</v>
+        <v>506457</v>
       </c>
       <c r="R31" t="n">
-        <v>7137328</v>
+        <v>7137369</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4088,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120454514</v>
+        <v>120454852</v>
       </c>
       <c r="B33" t="n">
-        <v>79652</v>
+        <v>79131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4100,25 +4095,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4128,10 +4123,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506386</v>
+        <v>506472</v>
       </c>
       <c r="R33" t="n">
-        <v>7137593</v>
+        <v>7137475</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4190,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120454291</v>
+        <v>120455240</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4206,21 +4201,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4230,13 +4225,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506401</v>
+        <v>506406</v>
       </c>
       <c r="R34" t="n">
-        <v>7137641</v>
+        <v>7137340</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4292,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120454446</v>
+        <v>120454696</v>
       </c>
       <c r="B35" t="n">
-        <v>79624</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4308,21 +4303,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4332,10 +4327,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506409</v>
+        <v>506430</v>
       </c>
       <c r="R35" t="n">
-        <v>7137583</v>
+        <v>7137522</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4394,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120454579</v>
+        <v>120454335</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4410,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4434,13 +4429,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506394</v>
+        <v>506408</v>
       </c>
       <c r="R36" t="n">
-        <v>7137587</v>
+        <v>7137649</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4496,10 +4491,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120455279</v>
+        <v>120454514</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>79652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4508,25 +4503,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4536,13 +4531,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506406</v>
+        <v>506386</v>
       </c>
       <c r="R37" t="n">
-        <v>7137298</v>
+        <v>7137593</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4598,10 +4593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454696</v>
+        <v>120454291</v>
       </c>
       <c r="B38" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506430</v>
+        <v>506401</v>
       </c>
       <c r="R38" t="n">
-        <v>7137522</v>
+        <v>7137641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4700,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120454335</v>
+        <v>120455183</v>
       </c>
       <c r="B39" t="n">
-        <v>95478</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4716,21 +4711,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506408</v>
+        <v>506424</v>
       </c>
       <c r="R39" t="n">
-        <v>7137649</v>
+        <v>7137367</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4776,6 +4771,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,7 +4802,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454245</v>
+        <v>120454262</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506382</v>
+        <v>506386</v>
       </c>
       <c r="R40" t="n">
-        <v>7137641</v>
+        <v>7137645</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120455339</v>
+        <v>120454579</v>
       </c>
       <c r="B41" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4921,25 +4921,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4949,13 +4949,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506407</v>
+        <v>506394</v>
       </c>
       <c r="R41" t="n">
-        <v>7137248</v>
+        <v>7137587</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454852</v>
+        <v>120454446</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5027,21 +5027,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506472</v>
+        <v>506409</v>
       </c>
       <c r="R42" t="n">
-        <v>7137475</v>
+        <v>7137583</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -3053,10 +3053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120455339</v>
+        <v>120454398</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
+        <v>90591</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3069,21 +3069,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3093,13 +3093,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506407</v>
+        <v>506414</v>
       </c>
       <c r="R23" t="n">
-        <v>7137248</v>
+        <v>7137627</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120454435</v>
+        <v>120455339</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,25 +3269,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506404</v>
+        <v>506407</v>
       </c>
       <c r="R25" t="n">
-        <v>7137583</v>
+        <v>7137248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120455376</v>
+        <v>120454696</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506425</v>
+        <v>506430</v>
       </c>
       <c r="R26" t="n">
-        <v>7137243</v>
+        <v>7137522</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120455279</v>
+        <v>120455249</v>
       </c>
       <c r="B27" t="n">
-        <v>78278</v>
+        <v>79658</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506406</v>
+        <v>506409</v>
       </c>
       <c r="R27" t="n">
-        <v>7137298</v>
+        <v>7137328</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120454245</v>
+        <v>120454852</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506382</v>
+        <v>506472</v>
       </c>
       <c r="R28" t="n">
-        <v>7137641</v>
+        <v>7137475</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3639,11 +3639,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3670,10 +3665,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120455249</v>
+        <v>120454435</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3682,25 +3677,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3710,13 +3705,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506409</v>
+        <v>506404</v>
       </c>
       <c r="R29" t="n">
-        <v>7137328</v>
+        <v>7137583</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,7 +3767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120454929</v>
+        <v>120455376</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3812,10 +3807,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506479</v>
+        <v>506425</v>
       </c>
       <c r="R30" t="n">
-        <v>7137395</v>
+        <v>7137243</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,10 +3869,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120455044</v>
+        <v>120455240</v>
       </c>
       <c r="B31" t="n">
-        <v>57473</v>
+        <v>79624</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3890,42 +3885,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506457</v>
+        <v>506406</v>
       </c>
       <c r="R31" t="n">
-        <v>7137369</v>
+        <v>7137340</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3981,10 +3971,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454398</v>
+        <v>120455183</v>
       </c>
       <c r="B32" t="n">
-        <v>90591</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3993,25 +3983,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4021,13 +4011,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506414</v>
+        <v>506424</v>
       </c>
       <c r="R32" t="n">
-        <v>7137627</v>
+        <v>7137367</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,6 +4047,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,10 +4078,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120454852</v>
+        <v>120454929</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,21 +4094,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,13 +4118,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506472</v>
+        <v>506479</v>
       </c>
       <c r="R33" t="n">
-        <v>7137475</v>
+        <v>7137395</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4185,10 +4180,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120455240</v>
+        <v>120454335</v>
       </c>
       <c r="B34" t="n">
-        <v>79624</v>
+        <v>95478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4201,21 +4196,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,13 +4220,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506406</v>
+        <v>506408</v>
       </c>
       <c r="R34" t="n">
-        <v>7137340</v>
+        <v>7137649</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120454696</v>
+        <v>120454245</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4303,21 +4298,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,13 +4322,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506430</v>
+        <v>506382</v>
       </c>
       <c r="R35" t="n">
-        <v>7137522</v>
+        <v>7137641</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4363,6 +4358,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,10 +4389,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120454335</v>
+        <v>120454262</v>
       </c>
       <c r="B36" t="n">
-        <v>95478</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4405,21 +4405,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4429,13 +4429,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506408</v>
+        <v>506386</v>
       </c>
       <c r="R36" t="n">
-        <v>7137649</v>
+        <v>7137645</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4465,6 +4465,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,10 +4496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120454514</v>
+        <v>120455279</v>
       </c>
       <c r="B37" t="n">
-        <v>79652</v>
+        <v>78278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4503,25 +4508,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4531,13 +4536,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506386</v>
+        <v>506406</v>
       </c>
       <c r="R37" t="n">
-        <v>7137593</v>
+        <v>7137298</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4593,10 +4598,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454291</v>
+        <v>120454446</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506401</v>
+        <v>506409</v>
       </c>
       <c r="R38" t="n">
-        <v>7137641</v>
+        <v>7137583</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,10 +4700,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120455183</v>
+        <v>120454514</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4707,25 +4712,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4735,13 +4740,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506424</v>
+        <v>506386</v>
       </c>
       <c r="R39" t="n">
-        <v>7137367</v>
+        <v>7137593</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4771,11 +4776,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,10 +4802,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454262</v>
+        <v>120454579</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506386</v>
+        <v>506394</v>
       </c>
       <c r="R40" t="n">
-        <v>7137645</v>
+        <v>7137587</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4878,11 +4878,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4909,7 +4904,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120454579</v>
+        <v>120454291</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -4949,13 +4944,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506394</v>
+        <v>506401</v>
       </c>
       <c r="R41" t="n">
-        <v>7137587</v>
+        <v>7137641</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5011,10 +5006,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454446</v>
+        <v>120455044</v>
       </c>
       <c r="B42" t="n">
-        <v>79624</v>
+        <v>57473</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5027,37 +5022,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506409</v>
+        <v>506457</v>
       </c>
       <c r="R42" t="n">
-        <v>7137583</v>
+        <v>7137369</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -3053,10 +3053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120454398</v>
+        <v>120455339</v>
       </c>
       <c r="B23" t="n">
-        <v>90591</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3069,21 +3069,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3093,13 +3093,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506414</v>
+        <v>506407</v>
       </c>
       <c r="R23" t="n">
-        <v>7137627</v>
+        <v>7137248</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120454691</v>
+        <v>120454398</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>90591</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3167,25 +3167,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>1205</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506429</v>
+        <v>506414</v>
       </c>
       <c r="R24" t="n">
-        <v>7137523</v>
+        <v>7137627</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120455339</v>
+        <v>120454691</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,25 +3269,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506407</v>
+        <v>506429</v>
       </c>
       <c r="R25" t="n">
-        <v>7137248</v>
+        <v>7137523</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7091315</v>
+        <v>120454335</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506401.8319187159</v>
+        <v>506408</v>
       </c>
       <c r="R2" t="n">
-        <v>7137650.58502598</v>
+        <v>7137649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,63 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Asprika hyggen &amp; naturskog. Lövrikt restbestånd, sammanhängande med större skogsbestånd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asp 50 cm, skadad. Intill murken grov asplåga utan arter</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111479730</v>
+        <v>111480035</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506636.7902023449</v>
+        <v>506552</v>
       </c>
       <c r="R3" t="n">
-        <v>7137086.695334492</v>
+        <v>7137138</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,19 +840,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Filippa Paperin, Jonathan Frendel, Signe Propst, Iris Elmér, Elias Blad, Elicia Olsson, Astrid Blomberg, Ivar Anderberg, Kai Strömberg, Melvin Lewin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111476582</v>
+        <v>120454691</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydvästra Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506514.3320663989</v>
+        <v>506429</v>
       </c>
       <c r="R4" t="n">
-        <v>7137155.308644285</v>
+        <v>7137523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111479726</v>
+        <v>120454398</v>
       </c>
       <c r="B5" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506523.1528918216</v>
+        <v>506414</v>
       </c>
       <c r="R5" t="n">
-        <v>7137086.451659708</v>
+        <v>7137627</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111479725</v>
+        <v>111479728</v>
       </c>
       <c r="B6" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506573.8724125003</v>
+        <v>506536</v>
       </c>
       <c r="R6" t="n">
-        <v>7137099.122253072</v>
+        <v>7137088</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,19 +1131,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111476587</v>
+        <v>111479729</v>
       </c>
       <c r="B7" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydvästra Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506399.4467280412</v>
+        <v>506570</v>
       </c>
       <c r="R7" t="n">
-        <v>7137130.808956717</v>
+        <v>7137095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,19 +1228,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111477159</v>
+        <v>111480182</v>
       </c>
       <c r="B8" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SV gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506548.1973901832</v>
+        <v>506613</v>
       </c>
       <c r="R8" t="n">
-        <v>7137138.920001913</v>
+        <v>7137092</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,19 +1325,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Karl Soler Kinnerbäck, Tore Dahlberg, Melvin Lewin, Elvira Klang, Elicia Olsson, Jonathan Frendel, Astrid Blomberg, Iris Elmér, Ivar Anderberg, Kai Strömberg, Signe Propst, Elias Blad</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Filippa Paperin, Jonathan Frendel, Signe Propst, Iris Elmér, Elias Blad, Elicia Olsson, Astrid Blomberg, Ivar Anderberg, Kai Strömberg, Melvin Lewin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111479727</v>
+        <v>120454446</v>
       </c>
       <c r="B9" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506615.9431346679</v>
+        <v>506409</v>
       </c>
       <c r="R9" t="n">
-        <v>7137099.645855149</v>
+        <v>7137583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111479731</v>
+        <v>120455240</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506570.8492999141</v>
+        <v>506406</v>
       </c>
       <c r="R10" t="n">
-        <v>7137093.05119953</v>
+        <v>7137340</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,62 +1536,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111479732</v>
+        <v>111476581</v>
       </c>
       <c r="B11" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Sydvästra Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506557.7929852068</v>
+        <v>506355</v>
       </c>
       <c r="R11" t="n">
-        <v>7137113.816059647</v>
+        <v>7137081</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,19 +1616,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,62 +1633,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111479729</v>
+        <v>111476582</v>
       </c>
       <c r="B12" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Sydvästra Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506569.97720399</v>
+        <v>506514</v>
       </c>
       <c r="R12" t="n">
-        <v>7137095.215254448</v>
+        <v>7137155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,19 +1713,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1936,16 +1745,11 @@
         <v>111476583</v>
       </c>
       <c r="B13" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1973,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506622.9155112779</v>
+        <v>506623</v>
       </c>
       <c r="R13" t="n">
-        <v>7137084.499428711</v>
+        <v>7137085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,19 +1810,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,50 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111476580</v>
+        <v>111479730</v>
       </c>
       <c r="B14" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sydvästra Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506446.2270308413</v>
+        <v>506637</v>
       </c>
       <c r="R14" t="n">
-        <v>7137160.362918839</v>
+        <v>7137087</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,19 +1907,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,62 +1924,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111476579</v>
+        <v>111479731</v>
       </c>
       <c r="B15" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sydvästra Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506411.5719905405</v>
+        <v>506571</v>
       </c>
       <c r="R15" t="n">
-        <v>7137139.931017525</v>
+        <v>7137093</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,19 +2004,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,49 +2021,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111479733</v>
+        <v>111480444</v>
       </c>
       <c r="B16" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506542.631959103</v>
+        <v>506552</v>
       </c>
       <c r="R16" t="n">
-        <v>7137104.68686779</v>
+        <v>7137138</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,19 +2101,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,62 +2118,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Tore Dahlberg, Elvira Klang, Elicia Olsson, Filippa Paperin, Jonathan Frendel, Karl Soler Kinnerbäck, Elias Blad, Signe Propst, Ivar Anderberg, Kai Strömberg, Astrid Blomberg, Melvin Lewin, Iris Elmér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111479728</v>
+        <v>120454291</v>
       </c>
       <c r="B17" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506536.1601844588</v>
+        <v>506401</v>
       </c>
       <c r="R17" t="n">
-        <v>7137088.645264999</v>
+        <v>7137641</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,22 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,31 +2215,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111480444</v>
+        <v>120454579</v>
       </c>
       <c r="B18" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2529,14 +2258,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506552.5373931379</v>
+        <v>506394</v>
       </c>
       <c r="R18" t="n">
-        <v>7137137.629731925</v>
+        <v>7137587</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2563,22 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,65 +2312,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Elvira Klang, Elicia Olsson, Filippa Paperin, Jonathan Frendel, Karl Soler Kinnerbäck, Elias Blad, Signe Propst, Ivar Anderberg, Kai Strömberg, Astrid Blomberg, Melvin Lewin, Iris Elmér</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111480182</v>
+        <v>120454929</v>
       </c>
       <c r="B19" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506612.9247734078</v>
+        <v>506479</v>
       </c>
       <c r="R19" t="n">
-        <v>7137091.40884747</v>
+        <v>7137395</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,22 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,65 +2409,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Filippa Paperin, Jonathan Frendel, Signe Propst, Iris Elmér, Elias Blad, Elicia Olsson, Astrid Blomberg, Ivar Anderberg, Kai Strömberg, Melvin Lewin, Elvira Klang</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111480140</v>
+        <v>120455376</v>
       </c>
       <c r="B20" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506612.9201057266</v>
+        <v>506425</v>
       </c>
       <c r="R20" t="n">
-        <v>7137093.574760968</v>
+        <v>7137243</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2787,22 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,27 +2506,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Filippa Paperin, Jonathan Frendel, Signe Propst, Iris Elmér, Elias Blad, Elicia Olsson, Astrid Blomberg, Ivar Anderberg, Kai Strömberg, Melvin Lewin, Elvira Klang</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111480041</v>
+        <v>111477159</v>
       </c>
       <c r="B21" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2865,17 +2549,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>SV Gärdvattnet, Jmt</t>
+          <t>SV gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506532.6737455213</v>
+        <v>506548</v>
       </c>
       <c r="R21" t="n">
-        <v>7137096.435164435</v>
+        <v>7137139</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,19 +2586,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,27 +2603,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Filippa Paperin, Jonathan Frendel, Signe Propst, Iris Elmér, Elias Blad, Elicia Olsson, Astrid Blomberg, Ivar Anderberg, Kai Strömberg, Melvin Lewin, Elvira Klang</t>
+          <t>Filippa Paperin, Karl Soler Kinnerbäck, Tore Dahlberg, Melvin Lewin, Elvira Klang, Elicia Olsson, Jonathan Frendel, Astrid Blomberg, Iris Elmér, Ivar Anderberg, Kai Strömberg, Signe Propst, Elias Blad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111480035</v>
+        <v>111480041</v>
       </c>
       <c r="B22" t="n">
-        <v>76513</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2957,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2981,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506552.5373931379</v>
+        <v>506533</v>
       </c>
       <c r="R22" t="n">
-        <v>7137137.629731925</v>
+        <v>7137097</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3014,19 +2683,9 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120455044</v>
+        <v>120455279</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,42 +2723,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506457</v>
+        <v>506406</v>
       </c>
       <c r="R23" t="n">
-        <v>7137369</v>
+        <v>7137298</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3160,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120455376</v>
+        <v>120454696</v>
       </c>
       <c r="B24" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3200,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506425</v>
+        <v>506430</v>
       </c>
       <c r="R24" t="n">
-        <v>7137243</v>
+        <v>7137522</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3262,50 +2906,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120454446</v>
+        <v>7091315</v>
       </c>
       <c r="B25" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>Söder Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506409</v>
+        <v>506402</v>
       </c>
       <c r="R25" t="n">
-        <v>7137583</v>
+        <v>7137651</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2013-08-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2013-08-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,31 +2987,36 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Asprika hyggen &amp; naturskog. Lövrikt restbestånd, sammanhängande med större skogsbestånd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Asp 50 cm, skadad. Intill murken grov asplåga utan arter</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120454696</v>
+        <v>120454435</v>
       </c>
       <c r="B26" t="n">
-        <v>79208</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3404,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506430</v>
+        <v>506404</v>
       </c>
       <c r="R26" t="n">
-        <v>7137522</v>
+        <v>7137583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3466,50 +3110,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120454691</v>
+        <v>111479726</v>
       </c>
       <c r="B27" t="n">
-        <v>78235</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506429</v>
+        <v>506523</v>
       </c>
       <c r="R27" t="n">
-        <v>7137523</v>
+        <v>7137086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,12 +3175,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,65 +3195,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120455183</v>
+        <v>111480140</v>
       </c>
       <c r="B28" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506424</v>
+        <v>506613</v>
       </c>
       <c r="R28" t="n">
-        <v>7137367</v>
+        <v>7137093</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3638,17 +3272,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,49 +3292,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Filippa Paperin, Jonathan Frendel, Signe Propst, Iris Elmér, Elias Blad, Elicia Olsson, Astrid Blomberg, Ivar Anderberg, Kai Strömberg, Melvin Lewin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120454335</v>
+        <v>120454514</v>
       </c>
       <c r="B29" t="n">
-        <v>95587</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,13 +3339,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506408</v>
+        <v>506386</v>
       </c>
       <c r="R29" t="n">
-        <v>7137649</v>
+        <v>7137593</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3780,12 +3404,7 @@
         <v>120455249</v>
       </c>
       <c r="B30" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,53 +3498,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120454852</v>
+        <v>111479727</v>
       </c>
       <c r="B31" t="n">
-        <v>79179</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506472</v>
+        <v>506616</v>
       </c>
       <c r="R31" t="n">
-        <v>7137475</v>
+        <v>7137100</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3949,12 +3571,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3969,27 +3591,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120454291</v>
+        <v>111479725</v>
       </c>
       <c r="B32" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,34 +3614,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506401</v>
+        <v>506574</v>
       </c>
       <c r="R32" t="n">
-        <v>7137641</v>
+        <v>7137099</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4051,12 +3676,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4071,27 +3696,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120455240</v>
+        <v>120454245</v>
       </c>
       <c r="B33" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4099,21 +3719,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4123,10 +3743,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506406</v>
+        <v>506382</v>
       </c>
       <c r="R33" t="n">
-        <v>7137340</v>
+        <v>7137641</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4159,6 +3779,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4185,15 +3810,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120454929</v>
+        <v>120454262</v>
       </c>
       <c r="B34" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,21 +3821,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4225,13 +3845,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506479</v>
+        <v>506386</v>
       </c>
       <c r="R34" t="n">
-        <v>7137395</v>
+        <v>7137645</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4261,6 +3881,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4287,15 +3912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120455279</v>
+        <v>120455183</v>
       </c>
       <c r="B35" t="n">
-        <v>78326</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,21 +3923,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506406</v>
+        <v>506424</v>
       </c>
       <c r="R35" t="n">
-        <v>7137298</v>
+        <v>7137367</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,6 +3983,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4389,53 +4014,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120454398</v>
+        <v>120523986</v>
       </c>
       <c r="B36" t="n">
-        <v>90681</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>Lidsjöberg, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506414</v>
+        <v>506423</v>
       </c>
       <c r="R36" t="n">
-        <v>7137627</v>
+        <v>7137364</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4465,6 +4085,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,53 +4116,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120455339</v>
+        <v>120455044</v>
       </c>
       <c r="B37" t="n">
-        <v>96994</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506407</v>
+        <v>506457</v>
       </c>
       <c r="R37" t="n">
-        <v>7137248</v>
+        <v>7137369</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4593,53 +4218,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120454579</v>
+        <v>111479732</v>
       </c>
       <c r="B38" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506394</v>
+        <v>506558</v>
       </c>
       <c r="R38" t="n">
-        <v>7137587</v>
+        <v>7137114</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4663,12 +4283,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4683,65 +4303,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120454245</v>
+        <v>111479733</v>
       </c>
       <c r="B39" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>SV Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506382</v>
+        <v>506543</v>
       </c>
       <c r="R39" t="n">
-        <v>7137641</v>
+        <v>7137105</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4765,17 +4380,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,49 +4400,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonathan Frendel, Astrid Blomberg, Elias Blad, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Kai Strömberg, Karl Soler Kinnerbäck, Melvin Lewin, Signe Propst, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120454435</v>
+        <v>120455339</v>
       </c>
       <c r="B40" t="n">
-        <v>79671</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4842,10 +4447,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506404</v>
+        <v>506407</v>
       </c>
       <c r="R40" t="n">
-        <v>7137583</v>
+        <v>7137248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,53 +4509,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120454262</v>
+        <v>111476577</v>
       </c>
       <c r="B41" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>Sydvästra Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506386</v>
+        <v>506400</v>
       </c>
       <c r="R41" t="n">
-        <v>7137645</v>
+        <v>7137131</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4974,17 +4574,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4999,27 +4594,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120454514</v>
+        <v>111476579</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,37 +4617,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
+          <t>Sydvästra Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506386</v>
+        <v>506411</v>
       </c>
       <c r="R42" t="n">
-        <v>7137593</v>
+        <v>7137140</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5081,12 +4671,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5101,27 +4691,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120523986</v>
+        <v>120454852</v>
       </c>
       <c r="B43" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5129,37 +4714,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lidsjöberg, Jmt</t>
+          <t>Gärdvattnet, Gärdvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506423</v>
+        <v>506472</v>
       </c>
       <c r="R43" t="n">
-        <v>7137364</v>
+        <v>7137475</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5189,11 +4774,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 31327-2023 artfynd.xlsx
+++ b/artfynd/A 31327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454335</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480035</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454691</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479728</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476581</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476582</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479731</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480444</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454291</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454579</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454929</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455376</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111477159</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480041</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455279</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454696</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7091315</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454435</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479726</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454514</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455249</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3212,6 +3342,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479725</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454245</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454262</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3518,6 +3663,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455183</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3620,6 +3770,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523986</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3722,6 +3877,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455044</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3819,6 +3979,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479732</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3916,6 +4081,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479733</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455339</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4110,6 +4285,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476577</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4207,6 +4387,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476579</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4304,6 +4489,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120454852</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4401,6 +4591,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480182</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4498,6 +4693,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111476583</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4595,6 +4795,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479730</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4692,6 +4897,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111480140</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4797,8 +5007,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111479727</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>